--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ideaWorkSpace\2.1.0\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
   </si>
@@ -78,10 +78,6 @@
   <si>
     <t>资产四级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前处理人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -443,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="15.5" customWidth="1"/>
@@ -459,7 +455,7 @@
     <col min="14" max="14" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -510,9 +506,6 @@
       </c>
       <c r="Q1" t="s">
         <v>11</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ideaWorkSpace\2.1.0\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\dcretams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>组合代码</t>
   </si>
@@ -78,6 +78,10 @@
   <si>
     <t>资产四级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -103,6 +107,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -439,72 +444,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="18.125" customWidth="1"/>
-    <col min="7" max="7" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="13.625" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="11.375" customWidth="1"/>
-    <col min="12" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="15.25" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="13.625" customWidth="1"/>
+    <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="12" width="11.375" customWidth="1"/>
+    <col min="13" max="14" width="11.25" customWidth="1"/>
+    <col min="15" max="15" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>11</v>
       </c>
     </row>
